--- a/VanHanhCD1/wwwroot/templates/BMVH_KhuKhiKhoiThieuKet1.xlsx
+++ b/VanHanhCD1/wwwroot/templates/BMVH_KhuKhiKhoiThieuKet1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\03. Project Hoa Phat\01. Keo Day\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02. Du An Hoa Phat\API\VanHanhCD1_API-release\VanHanhCD1\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E5D7D0-738A-4039-B2C6-1ECC1D7A9AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C59B89-D480-403C-A188-E443C45834F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,10 +19,19 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Sheet2!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1228,6 +1237,171 @@
     <xf numFmtId="164" fontId="24" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="9" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="9" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="9" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1249,24 +1423,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1282,9 +1444,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1294,182 +1453,32 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="9" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="9" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="9" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1517,7 +1526,7 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="329854" y="0"/>
-          <a:ext cx="2057400" cy="1163882"/>
+          <a:ext cx="2324100" cy="1163882"/>
           <a:chOff x="-22405" y="21571"/>
           <a:chExt cx="2095500" cy="857252"/>
         </a:xfrm>
@@ -2244,6 +2253,7 @@
   <dimension ref="A1:AJ38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
     <col min="4" max="4" width="8.42578125" customWidth="1"/>
     <col min="6" max="6" width="11.42578125" customWidth="1"/>
     <col min="7" max="7" width="10.42578125" customWidth="1"/>
@@ -2252,373 +2262,373 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="34"/>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="33"/>
-      <c r="AC1" s="33"/>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="33"/>
-      <c r="AF1" s="33"/>
-      <c r="AG1" s="33"/>
-      <c r="AH1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI1" s="32"/>
-      <c r="AJ1" s="32"/>
+      <c r="A1" s="89"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
+      <c r="R1" s="88"/>
+      <c r="S1" s="88"/>
+      <c r="T1" s="88"/>
+      <c r="U1" s="88"/>
+      <c r="V1" s="88"/>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="88"/>
+      <c r="Z1" s="88"/>
+      <c r="AA1" s="88"/>
+      <c r="AB1" s="88"/>
+      <c r="AC1" s="88"/>
+      <c r="AD1" s="88"/>
+      <c r="AE1" s="88"/>
+      <c r="AF1" s="88"/>
+      <c r="AG1" s="88"/>
+      <c r="AH1" s="87" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI1" s="87"/>
+      <c r="AJ1" s="87"/>
     </row>
     <row r="2" spans="1:36" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="33"/>
-      <c r="V2" s="33"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="33"/>
-      <c r="Y2" s="33"/>
-      <c r="Z2" s="33"/>
-      <c r="AA2" s="33"/>
-      <c r="AB2" s="33"/>
-      <c r="AC2" s="33"/>
-      <c r="AD2" s="33"/>
-      <c r="AE2" s="33"/>
-      <c r="AF2" s="33"/>
-      <c r="AG2" s="33"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
+      <c r="A2" s="89"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="88"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
+      <c r="W2" s="88"/>
+      <c r="X2" s="88"/>
+      <c r="Y2" s="88"/>
+      <c r="Z2" s="88"/>
+      <c r="AA2" s="88"/>
+      <c r="AB2" s="88"/>
+      <c r="AC2" s="88"/>
+      <c r="AD2" s="88"/>
+      <c r="AE2" s="88"/>
+      <c r="AF2" s="88"/>
+      <c r="AG2" s="88"/>
+      <c r="AH2" s="87"/>
+      <c r="AI2" s="87"/>
+      <c r="AJ2" s="87"/>
     </row>
     <row r="3" spans="1:36" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="84" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="30"/>
-      <c r="T3" s="30"/>
-      <c r="U3" s="30"/>
-      <c r="V3" s="30"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="30"/>
-      <c r="Z3" s="30"/>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="30"/>
-      <c r="AD3" s="30"/>
-      <c r="AE3" s="30"/>
-      <c r="AF3" s="30"/>
-      <c r="AG3" s="30"/>
-      <c r="AH3" s="30"/>
-      <c r="AI3" s="30"/>
-      <c r="AJ3" s="30"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="85"/>
+      <c r="Q3" s="85"/>
+      <c r="R3" s="85"/>
+      <c r="S3" s="85"/>
+      <c r="T3" s="85"/>
+      <c r="U3" s="85"/>
+      <c r="V3" s="85"/>
+      <c r="W3" s="85"/>
+      <c r="X3" s="85"/>
+      <c r="Y3" s="85"/>
+      <c r="Z3" s="85"/>
+      <c r="AA3" s="85"/>
+      <c r="AB3" s="85"/>
+      <c r="AC3" s="85"/>
+      <c r="AD3" s="85"/>
+      <c r="AE3" s="85"/>
+      <c r="AF3" s="85"/>
+      <c r="AG3" s="85"/>
+      <c r="AH3" s="85"/>
+      <c r="AI3" s="85"/>
+      <c r="AJ3" s="85"/>
     </row>
     <row r="4" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="31" t="s">
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="31"/>
-      <c r="O4" s="31"/>
-      <c r="P4" s="31"/>
-      <c r="Q4" s="31"/>
-      <c r="R4" s="31"/>
-      <c r="S4" s="31"/>
-      <c r="T4" s="31"/>
-      <c r="U4" s="31"/>
-      <c r="V4" s="31"/>
-      <c r="W4" s="31"/>
-      <c r="X4" s="31"/>
-      <c r="Y4" s="31"/>
-      <c r="Z4" s="31"/>
-      <c r="AA4" s="31"/>
-      <c r="AB4" s="31"/>
-      <c r="AC4" s="31"/>
-      <c r="AD4" s="31"/>
-      <c r="AE4" s="31"/>
-      <c r="AF4" s="31"/>
-      <c r="AG4" s="31"/>
-      <c r="AH4" s="31"/>
-      <c r="AI4" s="31"/>
-      <c r="AJ4" s="31"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="86"/>
+      <c r="K4" s="86"/>
+      <c r="L4" s="86"/>
+      <c r="M4" s="86"/>
+      <c r="N4" s="86"/>
+      <c r="O4" s="86"/>
+      <c r="P4" s="86"/>
+      <c r="Q4" s="86"/>
+      <c r="R4" s="86"/>
+      <c r="S4" s="86"/>
+      <c r="T4" s="86"/>
+      <c r="U4" s="86"/>
+      <c r="V4" s="86"/>
+      <c r="W4" s="86"/>
+      <c r="X4" s="86"/>
+      <c r="Y4" s="86"/>
+      <c r="Z4" s="86"/>
+      <c r="AA4" s="86"/>
+      <c r="AB4" s="86"/>
+      <c r="AC4" s="86"/>
+      <c r="AD4" s="86"/>
+      <c r="AE4" s="86"/>
+      <c r="AF4" s="86"/>
+      <c r="AG4" s="86"/>
+      <c r="AH4" s="86"/>
+      <c r="AI4" s="86"/>
+      <c r="AJ4" s="86"/>
     </row>
     <row r="5" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="82"/>
-      <c r="B5" s="83"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="41" t="s">
+      <c r="A5" s="32"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="37"/>
-      <c r="F5" s="41" t="s">
+      <c r="E5" s="31"/>
+      <c r="F5" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="37"/>
-      <c r="H5" s="41" t="s">
+      <c r="G5" s="31"/>
+      <c r="H5" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="37"/>
-      <c r="J5" s="99" t="s">
+      <c r="I5" s="31"/>
+      <c r="J5" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="100"/>
-      <c r="L5" s="80" t="s">
+      <c r="K5" s="52"/>
+      <c r="L5" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="M5" s="81"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="41" t="s">
+      <c r="M5" s="54"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="R5" s="36"/>
-      <c r="S5" s="37"/>
-      <c r="T5" s="41" t="s">
+      <c r="R5" s="30"/>
+      <c r="S5" s="31"/>
+      <c r="T5" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="U5" s="36"/>
-      <c r="V5" s="36"/>
-      <c r="W5" s="36"/>
-      <c r="X5" s="36"/>
-      <c r="Y5" s="36"/>
-      <c r="Z5" s="36"/>
-      <c r="AA5" s="37"/>
-      <c r="AB5" s="41" t="s">
+      <c r="U5" s="30"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="30"/>
+      <c r="X5" s="30"/>
+      <c r="Y5" s="30"/>
+      <c r="Z5" s="30"/>
+      <c r="AA5" s="31"/>
+      <c r="AB5" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="AC5" s="36"/>
-      <c r="AD5" s="36"/>
-      <c r="AE5" s="36"/>
-      <c r="AF5" s="36"/>
-      <c r="AG5" s="36"/>
-      <c r="AH5" s="36"/>
-      <c r="AI5" s="41" t="s">
+      <c r="AC5" s="30"/>
+      <c r="AD5" s="30"/>
+      <c r="AE5" s="30"/>
+      <c r="AF5" s="30"/>
+      <c r="AG5" s="30"/>
+      <c r="AH5" s="30"/>
+      <c r="AI5" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="AJ5" s="37"/>
+      <c r="AJ5" s="31"/>
     </row>
     <row r="6" spans="1:36" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="85"/>
-      <c r="B6" s="86"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="91" t="s">
+      <c r="A6" s="35"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="91" t="s">
+      <c r="E6" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="68" t="s">
+      <c r="F6" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="68" t="s">
+      <c r="G6" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="68" t="s">
+      <c r="H6" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="68" t="s">
+      <c r="I6" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="68" t="s">
+      <c r="J6" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="68" t="s">
+      <c r="K6" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="95" t="s">
+      <c r="L6" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="M6" s="95" t="s">
+      <c r="M6" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="N6" s="93" t="s">
+      <c r="N6" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="O6" s="95" t="s">
+      <c r="O6" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="P6" s="95" t="s">
+      <c r="P6" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="Q6" s="68" t="s">
+      <c r="Q6" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="R6" s="74" t="s">
+      <c r="R6" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="S6" s="68" t="s">
+      <c r="S6" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="T6" s="68" t="s">
+      <c r="T6" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="U6" s="97" t="s">
+      <c r="U6" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="V6" s="68" t="s">
+      <c r="V6" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="W6" s="76" t="s">
+      <c r="W6" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="X6" s="74" t="s">
+      <c r="X6" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="Y6" s="78" t="s">
+      <c r="Y6" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="Z6" s="68" t="s">
+      <c r="Z6" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AA6" s="78" t="s">
+      <c r="AA6" s="70" t="s">
         <v>30</v>
       </c>
       <c r="AB6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AC6" s="72" t="s">
+      <c r="AC6" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="AD6" s="68" t="s">
+      <c r="AD6" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="AE6" s="68" t="s">
+      <c r="AE6" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="AF6" s="68" t="s">
+      <c r="AF6" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="AG6" s="68" t="s">
+      <c r="AG6" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="AH6" s="74" t="s">
+      <c r="AH6" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="AI6" s="68" t="s">
+      <c r="AI6" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="AJ6" s="68" t="s">
+      <c r="AJ6" s="43" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="89"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="69"/>
-      <c r="L7" s="96"/>
-      <c r="M7" s="96"/>
-      <c r="N7" s="94"/>
-      <c r="O7" s="96"/>
-      <c r="P7" s="96"/>
-      <c r="Q7" s="69"/>
-      <c r="R7" s="75"/>
-      <c r="S7" s="69"/>
-      <c r="T7" s="69"/>
-      <c r="U7" s="98"/>
-      <c r="V7" s="69"/>
-      <c r="W7" s="77"/>
-      <c r="X7" s="75"/>
-      <c r="Y7" s="79"/>
-      <c r="Z7" s="69"/>
-      <c r="AA7" s="79"/>
+    <row r="7" spans="1:36" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="38"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="44"/>
+      <c r="R7" s="67"/>
+      <c r="S7" s="44"/>
+      <c r="T7" s="44"/>
+      <c r="U7" s="50"/>
+      <c r="V7" s="44"/>
+      <c r="W7" s="69"/>
+      <c r="X7" s="67"/>
+      <c r="Y7" s="71"/>
+      <c r="Z7" s="44"/>
+      <c r="AA7" s="71"/>
       <c r="AB7" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="AC7" s="73"/>
-      <c r="AD7" s="69"/>
-      <c r="AE7" s="69"/>
-      <c r="AF7" s="69"/>
-      <c r="AG7" s="69"/>
-      <c r="AH7" s="75"/>
-      <c r="AI7" s="69"/>
-      <c r="AJ7" s="69"/>
+      <c r="AC7" s="65"/>
+      <c r="AD7" s="44"/>
+      <c r="AE7" s="44"/>
+      <c r="AF7" s="44"/>
+      <c r="AG7" s="44"/>
+      <c r="AH7" s="67"/>
+      <c r="AI7" s="44"/>
+      <c r="AJ7" s="44"/>
     </row>
     <row r="8" spans="1:36" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="70" t="s">
+      <c r="B8" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="71"/>
+      <c r="C8" s="63"/>
       <c r="D8" s="4"/>
       <c r="E8" s="5"/>
       <c r="F8" s="7" t="s">
@@ -2714,11 +2724,11 @@
       </c>
     </row>
     <row r="9" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="63"/>
-      <c r="B9" s="66">
+      <c r="A9" s="59"/>
+      <c r="B9" s="55">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C9" s="67"/>
+      <c r="C9" s="56"/>
       <c r="D9" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A1)-1)</f>
         <v>0</v>
@@ -2853,11 +2863,11 @@
       </c>
     </row>
     <row r="10" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="64"/>
-      <c r="B10" s="61">
+      <c r="A10" s="60"/>
+      <c r="B10" s="57">
         <v>0.375</v>
       </c>
-      <c r="C10" s="62"/>
+      <c r="C10" s="58"/>
       <c r="D10" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A2)-1)</f>
         <v>0</v>
@@ -2992,11 +3002,11 @@
       </c>
     </row>
     <row r="11" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="64"/>
-      <c r="B11" s="66">
+      <c r="A11" s="60"/>
+      <c r="B11" s="55">
         <v>0.41666666666666669</v>
       </c>
-      <c r="C11" s="67"/>
+      <c r="C11" s="56"/>
       <c r="D11" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A3)-1)</f>
         <v>0</v>
@@ -3131,11 +3141,11 @@
       </c>
     </row>
     <row r="12" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="64"/>
-      <c r="B12" s="61">
+      <c r="A12" s="60"/>
+      <c r="B12" s="57">
         <v>0.45833333333333331</v>
       </c>
-      <c r="C12" s="62"/>
+      <c r="C12" s="58"/>
       <c r="D12" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A4)-1)</f>
         <v>0</v>
@@ -3270,11 +3280,11 @@
       </c>
     </row>
     <row r="13" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="64"/>
-      <c r="B13" s="66">
+      <c r="A13" s="60"/>
+      <c r="B13" s="55">
         <v>0.5</v>
       </c>
-      <c r="C13" s="67"/>
+      <c r="C13" s="56"/>
       <c r="D13" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A5)-1)</f>
         <v>0</v>
@@ -3409,11 +3419,11 @@
       </c>
     </row>
     <row r="14" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="64"/>
-      <c r="B14" s="61">
+      <c r="A14" s="60"/>
+      <c r="B14" s="57">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C14" s="62"/>
+      <c r="C14" s="58"/>
       <c r="D14" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A6)-1)</f>
         <v>0</v>
@@ -3548,11 +3558,11 @@
       </c>
     </row>
     <row r="15" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="64"/>
-      <c r="B15" s="66">
+      <c r="A15" s="60"/>
+      <c r="B15" s="55">
         <v>0.58333333333333337</v>
       </c>
-      <c r="C15" s="67"/>
+      <c r="C15" s="56"/>
       <c r="D15" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A7)-1)</f>
         <v>0</v>
@@ -3687,11 +3697,11 @@
       </c>
     </row>
     <row r="16" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="64"/>
-      <c r="B16" s="61">
+      <c r="A16" s="60"/>
+      <c r="B16" s="57">
         <v>0.625</v>
       </c>
-      <c r="C16" s="62"/>
+      <c r="C16" s="58"/>
       <c r="D16" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A8)-1)</f>
         <v>0</v>
@@ -3826,11 +3836,11 @@
       </c>
     </row>
     <row r="17" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="64"/>
-      <c r="B17" s="66">
+      <c r="A17" s="60"/>
+      <c r="B17" s="55">
         <v>0.66666666666666663</v>
       </c>
-      <c r="C17" s="67"/>
+      <c r="C17" s="56"/>
       <c r="D17" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A9)-1)</f>
         <v>0</v>
@@ -3965,11 +3975,11 @@
       </c>
     </row>
     <row r="18" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="64"/>
-      <c r="B18" s="61">
+      <c r="A18" s="60"/>
+      <c r="B18" s="57">
         <v>0.70833333333333337</v>
       </c>
-      <c r="C18" s="62"/>
+      <c r="C18" s="58"/>
       <c r="D18" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A10)-1)</f>
         <v>0</v>
@@ -4104,11 +4114,11 @@
       </c>
     </row>
     <row r="19" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="64"/>
-      <c r="B19" s="66">
+      <c r="A19" s="60"/>
+      <c r="B19" s="55">
         <v>0.75</v>
       </c>
-      <c r="C19" s="67"/>
+      <c r="C19" s="56"/>
       <c r="D19" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A11)-1)</f>
         <v>0</v>
@@ -4243,11 +4253,11 @@
       </c>
     </row>
     <row r="20" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="65"/>
-      <c r="B20" s="61">
+      <c r="A20" s="61"/>
+      <c r="B20" s="57">
         <v>0.79166666666666663</v>
       </c>
-      <c r="C20" s="62"/>
+      <c r="C20" s="58"/>
       <c r="D20" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A12)-1)</f>
         <v>0</v>
@@ -4382,11 +4392,11 @@
       </c>
     </row>
     <row r="21" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="63"/>
-      <c r="B21" s="66">
+      <c r="A21" s="59"/>
+      <c r="B21" s="55">
         <v>0.83333333333333337</v>
       </c>
-      <c r="C21" s="67"/>
+      <c r="C21" s="56"/>
       <c r="D21" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A13)-1)</f>
         <v>0</v>
@@ -4521,11 +4531,11 @@
       </c>
     </row>
     <row r="22" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="64"/>
-      <c r="B22" s="61">
+      <c r="A22" s="60"/>
+      <c r="B22" s="57">
         <v>0.875</v>
       </c>
-      <c r="C22" s="62"/>
+      <c r="C22" s="58"/>
       <c r="D22" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A14)-1)</f>
         <v>0</v>
@@ -4660,11 +4670,11 @@
       </c>
     </row>
     <row r="23" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="64"/>
-      <c r="B23" s="66">
+      <c r="A23" s="60"/>
+      <c r="B23" s="55">
         <v>0.91666666666666663</v>
       </c>
-      <c r="C23" s="67"/>
+      <c r="C23" s="56"/>
       <c r="D23" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A15)-1)</f>
         <v>0</v>
@@ -4799,11 +4809,11 @@
       </c>
     </row>
     <row r="24" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="64"/>
-      <c r="B24" s="61">
+      <c r="A24" s="60"/>
+      <c r="B24" s="57">
         <v>0.95833333333333337</v>
       </c>
-      <c r="C24" s="62"/>
+      <c r="C24" s="58"/>
       <c r="D24" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A16)-1)</f>
         <v>0</v>
@@ -4938,11 +4948,11 @@
       </c>
     </row>
     <row r="25" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="64"/>
-      <c r="B25" s="66">
-        <v>0</v>
-      </c>
-      <c r="C25" s="67"/>
+      <c r="A25" s="60"/>
+      <c r="B25" s="55">
+        <v>0</v>
+      </c>
+      <c r="C25" s="56"/>
       <c r="D25" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A17)-1)</f>
         <v>0</v>
@@ -5077,11 +5087,11 @@
       </c>
     </row>
     <row r="26" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="64"/>
-      <c r="B26" s="61">
+      <c r="A26" s="60"/>
+      <c r="B26" s="57">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="C26" s="62"/>
+      <c r="C26" s="58"/>
       <c r="D26" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A18)-1)</f>
         <v>0</v>
@@ -5216,11 +5226,11 @@
       </c>
     </row>
     <row r="27" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="64"/>
-      <c r="B27" s="66">
+      <c r="A27" s="60"/>
+      <c r="B27" s="55">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="C27" s="67"/>
+      <c r="C27" s="56"/>
       <c r="D27" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A19)-1)</f>
         <v>0</v>
@@ -5355,11 +5365,11 @@
       </c>
     </row>
     <row r="28" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="64"/>
-      <c r="B28" s="61">
+      <c r="A28" s="60"/>
+      <c r="B28" s="57">
         <v>0.125</v>
       </c>
-      <c r="C28" s="62"/>
+      <c r="C28" s="58"/>
       <c r="D28" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A20)-1)</f>
         <v>0</v>
@@ -5494,11 +5504,11 @@
       </c>
     </row>
     <row r="29" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="64"/>
-      <c r="B29" s="66">
+      <c r="A29" s="60"/>
+      <c r="B29" s="55">
         <v>0.16666666666666666</v>
       </c>
-      <c r="C29" s="67"/>
+      <c r="C29" s="56"/>
       <c r="D29" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A21)-1)</f>
         <v>0</v>
@@ -5633,11 +5643,11 @@
       </c>
     </row>
     <row r="30" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="64"/>
-      <c r="B30" s="61">
+      <c r="A30" s="60"/>
+      <c r="B30" s="57">
         <v>0.20833333333333334</v>
       </c>
-      <c r="C30" s="62"/>
+      <c r="C30" s="58"/>
       <c r="D30" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A22)-1)</f>
         <v>0</v>
@@ -5772,11 +5782,11 @@
       </c>
     </row>
     <row r="31" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="64"/>
-      <c r="B31" s="66">
+      <c r="A31" s="60"/>
+      <c r="B31" s="55">
         <v>0.25</v>
       </c>
-      <c r="C31" s="67"/>
+      <c r="C31" s="56"/>
       <c r="D31" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A23)-1)</f>
         <v>0</v>
@@ -5911,11 +5921,11 @@
       </c>
     </row>
     <row r="32" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="65"/>
-      <c r="B32" s="66">
+      <c r="A32" s="61"/>
+      <c r="B32" s="55">
         <v>0.29166666666666669</v>
       </c>
-      <c r="C32" s="67"/>
+      <c r="C32" s="56"/>
       <c r="D32" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A24)-1)</f>
         <v>0</v>
@@ -6050,180 +6060,180 @@
       </c>
     </row>
     <row r="33" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="41" t="s">
+      <c r="A33" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="B33" s="39"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="53"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="53"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="53"/>
-      <c r="L33" s="54"/>
-      <c r="M33" s="54"/>
-      <c r="N33" s="53"/>
-      <c r="O33" s="53"/>
-      <c r="P33" s="53"/>
-      <c r="Q33" s="53"/>
-      <c r="R33" s="53"/>
-      <c r="S33" s="53"/>
-      <c r="T33" s="53"/>
-      <c r="U33" s="55"/>
-      <c r="V33" s="52"/>
-      <c r="W33" s="53"/>
-      <c r="X33" s="53"/>
-      <c r="Y33" s="53"/>
-      <c r="Z33" s="53"/>
-      <c r="AA33" s="53"/>
-      <c r="AB33" s="53"/>
-      <c r="AC33" s="53"/>
-      <c r="AD33" s="53"/>
-      <c r="AE33" s="53"/>
-      <c r="AF33" s="53"/>
-      <c r="AG33" s="53"/>
-      <c r="AH33" s="53"/>
-      <c r="AI33" s="53"/>
-      <c r="AJ33" s="56"/>
+      <c r="B33" s="72"/>
+      <c r="C33" s="73"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="75"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="75"/>
+      <c r="H33" s="75"/>
+      <c r="I33" s="75"/>
+      <c r="J33" s="75"/>
+      <c r="K33" s="75"/>
+      <c r="L33" s="76"/>
+      <c r="M33" s="76"/>
+      <c r="N33" s="75"/>
+      <c r="O33" s="75"/>
+      <c r="P33" s="75"/>
+      <c r="Q33" s="75"/>
+      <c r="R33" s="75"/>
+      <c r="S33" s="75"/>
+      <c r="T33" s="75"/>
+      <c r="U33" s="77"/>
+      <c r="V33" s="74"/>
+      <c r="W33" s="75"/>
+      <c r="X33" s="75"/>
+      <c r="Y33" s="75"/>
+      <c r="Z33" s="75"/>
+      <c r="AA33" s="75"/>
+      <c r="AB33" s="75"/>
+      <c r="AC33" s="75"/>
+      <c r="AD33" s="75"/>
+      <c r="AE33" s="75"/>
+      <c r="AF33" s="75"/>
+      <c r="AG33" s="75"/>
+      <c r="AH33" s="75"/>
+      <c r="AI33" s="75"/>
+      <c r="AJ33" s="78"/>
     </row>
     <row r="34" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="57" t="s">
+      <c r="A34" s="79" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="58"/>
-      <c r="C34" s="47" t="s">
+      <c r="B34" s="80"/>
+      <c r="C34" s="81" t="s">
         <v>78</v>
       </c>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="37"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="31"/>
       <c r="L34" s="2"/>
-      <c r="M34" s="36" t="s">
+      <c r="M34" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="N34" s="36"/>
-      <c r="O34" s="36"/>
-      <c r="P34" s="36"/>
-      <c r="Q34" s="36"/>
-      <c r="R34" s="36"/>
-      <c r="S34" s="36"/>
-      <c r="T34" s="36"/>
-      <c r="U34" s="37"/>
-      <c r="V34" s="57" t="s">
+      <c r="N34" s="30"/>
+      <c r="O34" s="30"/>
+      <c r="P34" s="30"/>
+      <c r="Q34" s="30"/>
+      <c r="R34" s="30"/>
+      <c r="S34" s="30"/>
+      <c r="T34" s="30"/>
+      <c r="U34" s="31"/>
+      <c r="V34" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="W34" s="59"/>
-      <c r="X34" s="60"/>
-      <c r="Y34" s="36"/>
-      <c r="Z34" s="36"/>
-      <c r="AA34" s="36"/>
-      <c r="AB34" s="36"/>
-      <c r="AC34" s="36"/>
-      <c r="AD34" s="36"/>
-      <c r="AE34" s="37"/>
-      <c r="AF34" s="41" t="s">
+      <c r="W34" s="82"/>
+      <c r="X34" s="83"/>
+      <c r="Y34" s="30"/>
+      <c r="Z34" s="30"/>
+      <c r="AA34" s="30"/>
+      <c r="AB34" s="30"/>
+      <c r="AC34" s="30"/>
+      <c r="AD34" s="30"/>
+      <c r="AE34" s="31"/>
+      <c r="AF34" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="AG34" s="36"/>
-      <c r="AH34" s="36"/>
-      <c r="AI34" s="36"/>
-      <c r="AJ34" s="37"/>
+      <c r="AG34" s="30"/>
+      <c r="AH34" s="30"/>
+      <c r="AI34" s="30"/>
+      <c r="AJ34" s="31"/>
     </row>
     <row r="35" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="49"/>
-      <c r="B35" s="50"/>
-      <c r="C35" s="47" t="s">
+      <c r="A35" s="99"/>
+      <c r="B35" s="100"/>
+      <c r="C35" s="81" t="s">
         <v>82</v>
       </c>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="36"/>
-      <c r="K35" s="48"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="98"/>
+      <c r="I35" s="81"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="98"/>
       <c r="L35" s="2"/>
-      <c r="M35" s="36" t="s">
+      <c r="M35" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="N35" s="36"/>
-      <c r="O35" s="36"/>
-      <c r="P35" s="36"/>
-      <c r="Q35" s="36"/>
-      <c r="R35" s="37"/>
-      <c r="S35" s="36"/>
-      <c r="T35" s="36"/>
-      <c r="U35" s="37"/>
-      <c r="V35" s="42"/>
-      <c r="W35" s="43"/>
-      <c r="X35" s="44"/>
-      <c r="Y35" s="36"/>
-      <c r="Z35" s="36"/>
-      <c r="AA35" s="36"/>
-      <c r="AB35" s="37"/>
-      <c r="AC35" s="36"/>
-      <c r="AD35" s="36"/>
-      <c r="AE35" s="37"/>
-      <c r="AF35" s="41" t="s">
+      <c r="N35" s="30"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="30"/>
+      <c r="Q35" s="30"/>
+      <c r="R35" s="31"/>
+      <c r="S35" s="30"/>
+      <c r="T35" s="30"/>
+      <c r="U35" s="31"/>
+      <c r="V35" s="93"/>
+      <c r="W35" s="94"/>
+      <c r="X35" s="95"/>
+      <c r="Y35" s="30"/>
+      <c r="Z35" s="30"/>
+      <c r="AA35" s="30"/>
+      <c r="AB35" s="31"/>
+      <c r="AC35" s="30"/>
+      <c r="AD35" s="30"/>
+      <c r="AE35" s="31"/>
+      <c r="AF35" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="AG35" s="36"/>
-      <c r="AH35" s="37"/>
-      <c r="AI35" s="36"/>
-      <c r="AJ35" s="37"/>
+      <c r="AG35" s="30"/>
+      <c r="AH35" s="31"/>
+      <c r="AI35" s="30"/>
+      <c r="AJ35" s="31"/>
     </row>
     <row r="36" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="45"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="47" t="s">
+      <c r="A36" s="96"/>
+      <c r="B36" s="97"/>
+      <c r="C36" s="81" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="47"/>
-      <c r="J36" s="36"/>
-      <c r="K36" s="48"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="98"/>
+      <c r="I36" s="81"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="98"/>
       <c r="L36" s="2"/>
-      <c r="M36" s="36" t="s">
+      <c r="M36" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="N36" s="36"/>
-      <c r="O36" s="36"/>
-      <c r="P36" s="36"/>
-      <c r="Q36" s="36"/>
-      <c r="R36" s="37"/>
-      <c r="S36" s="36"/>
-      <c r="T36" s="36"/>
-      <c r="U36" s="37"/>
-      <c r="V36" s="38"/>
-      <c r="W36" s="39"/>
-      <c r="X36" s="40"/>
-      <c r="Y36" s="36"/>
-      <c r="Z36" s="36"/>
-      <c r="AA36" s="36"/>
-      <c r="AB36" s="37"/>
-      <c r="AC36" s="36"/>
-      <c r="AD36" s="36"/>
-      <c r="AE36" s="37"/>
-      <c r="AF36" s="41" t="s">
+      <c r="N36" s="30"/>
+      <c r="O36" s="30"/>
+      <c r="P36" s="30"/>
+      <c r="Q36" s="30"/>
+      <c r="R36" s="31"/>
+      <c r="S36" s="30"/>
+      <c r="T36" s="30"/>
+      <c r="U36" s="31"/>
+      <c r="V36" s="91"/>
+      <c r="W36" s="72"/>
+      <c r="X36" s="92"/>
+      <c r="Y36" s="30"/>
+      <c r="Z36" s="30"/>
+      <c r="AA36" s="30"/>
+      <c r="AB36" s="31"/>
+      <c r="AC36" s="30"/>
+      <c r="AD36" s="30"/>
+      <c r="AE36" s="31"/>
+      <c r="AF36" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="AG36" s="36"/>
-      <c r="AH36" s="37"/>
-      <c r="AI36" s="36"/>
-      <c r="AJ36" s="37"/>
+      <c r="AG36" s="30"/>
+      <c r="AH36" s="31"/>
+      <c r="AI36" s="30"/>
+      <c r="AJ36" s="31"/>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
@@ -6268,6 +6278,86 @@
     </row>
   </sheetData>
   <mergeCells count="104">
+    <mergeCell ref="A3:AJ3"/>
+    <mergeCell ref="E4:AJ4"/>
+    <mergeCell ref="AH1:AJ2"/>
+    <mergeCell ref="E1:AG2"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="S36:U36"/>
+    <mergeCell ref="V36:X36"/>
+    <mergeCell ref="Y36:AB36"/>
+    <mergeCell ref="AC36:AE36"/>
+    <mergeCell ref="AF36:AH36"/>
+    <mergeCell ref="AI36:AJ36"/>
+    <mergeCell ref="V35:X35"/>
+    <mergeCell ref="Y35:AB35"/>
+    <mergeCell ref="AC35:AE35"/>
+    <mergeCell ref="AF35:AH35"/>
+    <mergeCell ref="AI35:AJ35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="M36:R36"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="M35:R35"/>
+    <mergeCell ref="S35:U35"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:U33"/>
+    <mergeCell ref="V33:AJ33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:K34"/>
+    <mergeCell ref="M34:U34"/>
+    <mergeCell ref="V34:X34"/>
+    <mergeCell ref="Y34:AE34"/>
+    <mergeCell ref="AF34:AJ34"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="A21:A32"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="AI6:AI7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="AC6:AC7"/>
+    <mergeCell ref="AD6:AD7"/>
+    <mergeCell ref="AE6:AE7"/>
+    <mergeCell ref="AF6:AF7"/>
+    <mergeCell ref="AG6:AG7"/>
+    <mergeCell ref="AH6:AH7"/>
+    <mergeCell ref="W6:W7"/>
+    <mergeCell ref="X6:X7"/>
+    <mergeCell ref="Y6:Y7"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="L5:P5"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="T5:AA5"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="A9:A20"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="AB5:AH5"/>
     <mergeCell ref="AI5:AJ5"/>
     <mergeCell ref="A5:C7"/>
@@ -6292,86 +6382,6 @@
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:P5"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="T5:AA5"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="A9:A20"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="AI6:AI7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="AC6:AC7"/>
-    <mergeCell ref="AD6:AD7"/>
-    <mergeCell ref="AE6:AE7"/>
-    <mergeCell ref="AF6:AF7"/>
-    <mergeCell ref="AG6:AG7"/>
-    <mergeCell ref="AH6:AH7"/>
-    <mergeCell ref="W6:W7"/>
-    <mergeCell ref="X6:X7"/>
-    <mergeCell ref="Y6:Y7"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="Q6:Q7"/>
-    <mergeCell ref="R6:R7"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="A21:A32"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="M35:R35"/>
-    <mergeCell ref="S35:U35"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:U33"/>
-    <mergeCell ref="V33:AJ33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:K34"/>
-    <mergeCell ref="M34:U34"/>
-    <mergeCell ref="V34:X34"/>
-    <mergeCell ref="Y34:AE34"/>
-    <mergeCell ref="AF34:AJ34"/>
-    <mergeCell ref="A3:AJ3"/>
-    <mergeCell ref="E4:AJ4"/>
-    <mergeCell ref="AH1:AJ2"/>
-    <mergeCell ref="E1:AG2"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="S36:U36"/>
-    <mergeCell ref="V36:X36"/>
-    <mergeCell ref="Y36:AB36"/>
-    <mergeCell ref="AC36:AE36"/>
-    <mergeCell ref="AF36:AH36"/>
-    <mergeCell ref="AI36:AJ36"/>
-    <mergeCell ref="V35:X35"/>
-    <mergeCell ref="Y35:AB35"/>
-    <mergeCell ref="AC35:AE35"/>
-    <mergeCell ref="AF35:AH35"/>
-    <mergeCell ref="AI35:AJ35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="M36:R36"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:H35"/>
-    <mergeCell ref="I35:K35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="26" orientation="landscape" r:id="rId1"/>
@@ -6390,9 +6400,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="101"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
       <c r="D1" s="22"/>
       <c r="E1" s="22"/>
       <c r="F1" s="22"/>
@@ -6407,58 +6417,58 @@
       <c r="O1" s="22"/>
       <c r="P1" s="22"/>
       <c r="Q1" s="22"/>
-      <c r="R1" s="107" t="s">
+      <c r="R1" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="101"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
       <c r="D2" s="22"/>
-      <c r="E2" s="108" t="s">
+      <c r="E2" s="103" t="s">
         <v>99</v>
       </c>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="108"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="108"/>
-      <c r="M2" s="108"/>
-      <c r="N2" s="108"/>
-      <c r="O2" s="108"/>
-      <c r="P2" s="108"/>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="109" t="s">
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="103"/>
+      <c r="R2" s="104" t="s">
         <v>90</v>
       </c>
-      <c r="S2" s="109"/>
-      <c r="T2" s="109"/>
-      <c r="U2" s="109"/>
+      <c r="S2" s="104"/>
+      <c r="T2" s="104"/>
+      <c r="U2" s="104"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A3" s="106"/>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
+      <c r="A3" s="101"/>
+      <c r="B3" s="101"/>
+      <c r="C3" s="101"/>
       <c r="D3" s="22"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="108"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="108"/>
-      <c r="K3" s="108"/>
-      <c r="L3" s="108"/>
-      <c r="M3" s="108"/>
-      <c r="N3" s="108"/>
-      <c r="O3" s="108"/>
-      <c r="P3" s="108"/>
-      <c r="Q3" s="108"/>
+      <c r="E3" s="103"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="103"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="103"/>
+      <c r="N3" s="103"/>
+      <c r="O3" s="103"/>
+      <c r="P3" s="103"/>
+      <c r="Q3" s="103"/>
       <c r="R3" s="22"/>
       <c r="S3" s="22"/>
       <c r="T3" s="22"/>
@@ -6490,10 +6500,10 @@
       <c r="U4" s="24"/>
     </row>
     <row r="5" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="104" t="s">
+      <c r="A5" s="108" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="105"/>
+      <c r="B5" s="109"/>
       <c r="C5" s="25" t="s">
         <v>93</v>
       </c>
@@ -6571,7 +6581,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A6" s="101" t="s">
+      <c r="A6" s="105" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="26" t="s">
@@ -6606,7 +6616,7 @@
       <c r="AA6" s="26"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A7" s="103"/>
+      <c r="A7" s="106"/>
       <c r="B7" s="26" t="s">
         <v>13</v>
       </c>
@@ -6639,7 +6649,7 @@
       <c r="AA7" s="26"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A8" s="101" t="s">
+      <c r="A8" s="105" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="26" t="s">
@@ -6674,7 +6684,7 @@
       <c r="AA8" s="26"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A9" s="103"/>
+      <c r="A9" s="106"/>
       <c r="B9" s="26" t="s">
         <v>15</v>
       </c>
@@ -6707,7 +6717,7 @@
       <c r="AA9" s="26"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A10" s="101" t="s">
+      <c r="A10" s="105" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="26" t="s">
@@ -6742,7 +6752,7 @@
       <c r="AA10" s="26"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A11" s="103"/>
+      <c r="A11" s="106"/>
       <c r="B11" s="26" t="s">
         <v>15</v>
       </c>
@@ -6775,7 +6785,7 @@
       <c r="AA11" s="26"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A12" s="101" t="s">
+      <c r="A12" s="105" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="26" t="s">
@@ -6810,7 +6820,7 @@
       <c r="AA12" s="26"/>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A13" s="103"/>
+      <c r="A13" s="106"/>
       <c r="B13" s="26" t="s">
         <v>15</v>
       </c>
@@ -6843,7 +6853,7 @@
       <c r="AA13" s="26"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A14" s="101" t="s">
+      <c r="A14" s="105" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="26" t="s">
@@ -6878,7 +6888,7 @@
       <c r="AA14" s="26"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A15" s="102"/>
+      <c r="A15" s="107"/>
       <c r="B15" s="26" t="s">
         <v>18</v>
       </c>
@@ -6911,7 +6921,7 @@
       <c r="AA15" s="26"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A16" s="102"/>
+      <c r="A16" s="107"/>
       <c r="B16" s="26" t="s">
         <v>19</v>
       </c>
@@ -6944,7 +6954,7 @@
       <c r="AA16" s="26"/>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A17" s="102"/>
+      <c r="A17" s="107"/>
       <c r="B17" s="26" t="s">
         <v>20</v>
       </c>
@@ -6977,7 +6987,7 @@
       <c r="AA17" s="26"/>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A18" s="103"/>
+      <c r="A18" s="106"/>
       <c r="B18" s="26" t="s">
         <v>21</v>
       </c>
@@ -7010,7 +7020,7 @@
       <c r="AA18" s="26"/>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A19" s="101" t="s">
+      <c r="A19" s="105" t="s">
         <v>8</v>
       </c>
       <c r="B19" s="26" t="s">
@@ -7045,7 +7055,7 @@
       <c r="AA19" s="26"/>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A20" s="102"/>
+      <c r="A20" s="107"/>
       <c r="B20" s="26" t="s">
         <v>15</v>
       </c>
@@ -7078,7 +7088,7 @@
       <c r="AA20" s="26"/>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A21" s="103"/>
+      <c r="A21" s="106"/>
       <c r="B21" s="26" t="s">
         <v>22</v>
       </c>
@@ -7111,7 +7121,7 @@
       <c r="AA21" s="26"/>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A22" s="101" t="s">
+      <c r="A22" s="105" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="26" t="s">
@@ -7146,7 +7156,7 @@
       <c r="AA22" s="26"/>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A23" s="102"/>
+      <c r="A23" s="107"/>
       <c r="B23" s="26" t="s">
         <v>24</v>
       </c>
@@ -7179,7 +7189,7 @@
       <c r="AA23" s="26"/>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A24" s="102"/>
+      <c r="A24" s="107"/>
       <c r="B24" s="26" t="s">
         <v>25</v>
       </c>
@@ -7212,7 +7222,7 @@
       <c r="AA24" s="26"/>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A25" s="102"/>
+      <c r="A25" s="107"/>
       <c r="B25" s="26" t="s">
         <v>26</v>
       </c>
@@ -7245,7 +7255,7 @@
       <c r="AA25" s="26"/>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A26" s="102"/>
+      <c r="A26" s="107"/>
       <c r="B26" s="26" t="s">
         <v>27</v>
       </c>
@@ -7278,7 +7288,7 @@
       <c r="AA26" s="26"/>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A27" s="102"/>
+      <c r="A27" s="107"/>
       <c r="B27" s="26" t="s">
         <v>28</v>
       </c>
@@ -7311,7 +7321,7 @@
       <c r="AA27" s="26"/>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A28" s="102"/>
+      <c r="A28" s="107"/>
       <c r="B28" s="26" t="s">
         <v>29</v>
       </c>
@@ -7344,7 +7354,7 @@
       <c r="AA28" s="26"/>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A29" s="103"/>
+      <c r="A29" s="106"/>
       <c r="B29" s="26" t="s">
         <v>30</v>
       </c>
@@ -7377,7 +7387,7 @@
       <c r="AA29" s="26"/>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A30" s="101" t="s">
+      <c r="A30" s="105" t="s">
         <v>10</v>
       </c>
       <c r="B30" s="26" t="s">
@@ -7412,7 +7422,7 @@
       <c r="AA30" s="26"/>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A31" s="102"/>
+      <c r="A31" s="107"/>
       <c r="B31" s="26" t="s">
         <v>32</v>
       </c>
@@ -7445,7 +7455,7 @@
       <c r="AA31" s="26"/>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A32" s="102"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="26" t="s">
         <v>33</v>
       </c>
@@ -7478,7 +7488,7 @@
       <c r="AA32" s="26"/>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A33" s="102"/>
+      <c r="A33" s="107"/>
       <c r="B33" s="26" t="s">
         <v>34</v>
       </c>
@@ -7511,7 +7521,7 @@
       <c r="AA33" s="26"/>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A34" s="102"/>
+      <c r="A34" s="107"/>
       <c r="B34" s="26" t="s">
         <v>95</v>
       </c>
@@ -7544,7 +7554,7 @@
       <c r="AA34" s="26"/>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A35" s="102"/>
+      <c r="A35" s="107"/>
       <c r="B35" s="26" t="s">
         <v>96</v>
       </c>
@@ -7577,7 +7587,7 @@
       <c r="AA35" s="26"/>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A36" s="102"/>
+      <c r="A36" s="107"/>
       <c r="B36" s="26" t="s">
         <v>97</v>
       </c>
@@ -7610,7 +7620,7 @@
       <c r="AA36" s="26"/>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A37" s="102"/>
+      <c r="A37" s="107"/>
       <c r="B37" s="26" t="s">
         <v>38</v>
       </c>
@@ -7643,7 +7653,7 @@
       <c r="AA37" s="26"/>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A38" s="103"/>
+      <c r="A38" s="106"/>
       <c r="B38" s="26" t="s">
         <v>39</v>
       </c>
@@ -7677,11 +7687,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="E2:Q3"/>
-    <mergeCell ref="R2:U2"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A22:A29"/>
@@ -7690,6 +7695,11 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="E2:Q3"/>
+    <mergeCell ref="R2:U2"/>
+    <mergeCell ref="A6:A7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="35" orientation="landscape" r:id="rId1"/>
